--- a/herramientas/datos/pistas_propias.xlsx
+++ b/herramientas/datos/pistas_propias.xlsx
@@ -1,57 +1,315 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tativ\OneDrive\Documentos\Web Sagrada Familia Joven\Web - jovenes-sagrada-familia\herramientas\datos\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F264D846-5506-4A9E-BAB7-D42059ECE5DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Pistas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cómo cargar" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Pistas" sheetId="1" r:id="rId1"/>
+    <sheet name="Cómo cargar" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+  <si>
+    <t>Respuesta</t>
+  </si>
+  <si>
+    <t>Pista</t>
+  </si>
+  <si>
+    <t>Categoría</t>
+  </si>
+  <si>
+    <t>Pistas propias del crucigrama de la web</t>
+  </si>
+  <si>
+    <t>Una pista por fila, en la hoja «Pistas». La primera fila (títulos) no se toca.</t>
+  </si>
+  <si>
+    <t>Respuesta: la palabra que va en la grilla. Entre 3 y 11 letras. Las tildes y espacios se sacan solos (la Ñ queda).</t>
+  </si>
+  <si>
+    <t>Pista: lo que lee el jugador. Marcá el hueco con ___ (tres guiones bajos) y dejá palabras después del hueco.</t>
+  </si>
+  <si>
+    <t>Categoría: opcional (por ejemplo «Canciones»). Sirve para ordenar; no se muestra en el juego.</t>
+  </si>
+  <si>
+    <t>Para publicar: guardá y cerrá este Excel y hacé doble clic en «Actualizar crucigrama.bat» (en la carpeta de la web).</t>
+  </si>
+  <si>
+    <t>Los crucigramas que ya salieron no cambian: las pistas nuevas aparecen desde mañana.</t>
+  </si>
+  <si>
+    <t>Si una fila tiene un error (respuesta muy corta o sin pista), el programa la saltea y te avisa qué fila es.</t>
+  </si>
+  <si>
+    <t>LLAGAS</t>
+  </si>
+  <si>
+    <t>PIES</t>
+  </si>
+  <si>
+    <t>HONDO</t>
+  </si>
+  <si>
+    <t>CORAZON</t>
+  </si>
+  <si>
+    <t>CASA</t>
+  </si>
+  <si>
+    <t>DOLOR</t>
+  </si>
+  <si>
+    <t>CALLADO</t>
+  </si>
+  <si>
+    <t>CAMINAR</t>
+  </si>
+  <si>
+    <t>TRONO</t>
+  </si>
+  <si>
+    <t>AMADO</t>
+  </si>
+  <si>
+    <t>NOMBRE</t>
+  </si>
+  <si>
+    <t>INTERIOR</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>GRITAR</t>
+  </si>
+  <si>
+    <t>PERFUME</t>
+  </si>
+  <si>
+    <t>SANTO</t>
+  </si>
+  <si>
+    <t>CADENAS</t>
+  </si>
+  <si>
+    <t>RIO</t>
+  </si>
+  <si>
+    <t>PRESENCIA</t>
+  </si>
+  <si>
+    <t>ABUNDANCIA</t>
+  </si>
+  <si>
+    <t>ADORARTE</t>
+  </si>
+  <si>
+    <t>ELEVADO</t>
+  </si>
+  <si>
+    <t>MUNDO</t>
+  </si>
+  <si>
+    <t>JERUSALEN</t>
+  </si>
+  <si>
+    <t>HURACAN</t>
+  </si>
+  <si>
+    <t>SENTIR</t>
+  </si>
+  <si>
+    <t>BAILA</t>
+  </si>
+  <si>
+    <t>TEMPLO</t>
+  </si>
+  <si>
+    <t>GRITA</t>
+  </si>
+  <si>
+    <t>MUEVETE</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>PERDERE</t>
+  </si>
+  <si>
+    <t>AMOR</t>
+  </si>
+  <si>
+    <t>Canción: "Dentro de tus ___, escóndeme"</t>
+  </si>
+  <si>
+    <t>Canción: "Solo beso sus ___ Y a Dios se lo ofreció"</t>
+  </si>
+  <si>
+    <t>Canción: "Ama hasta lo más ___, de nuestra condición"</t>
+  </si>
+  <si>
+    <t>Canción: "Conozco tu ___, conozco tu realidad"</t>
+  </si>
+  <si>
+    <t>Canción: "Vuelve a ___ hoy, vuelve por favor"</t>
+  </si>
+  <si>
+    <t>Canción: "Ayúdame a cargar tanto ___"</t>
+  </si>
+  <si>
+    <t>Canción: "Dime rey por qué estás tan ___"</t>
+  </si>
+  <si>
+    <t>Canción: "Desde entonces lo he visto ___ a mi lado"</t>
+  </si>
+  <si>
+    <t>Canción: "Frente a tu ___ Señor, traigo mi corazón"</t>
+  </si>
+  <si>
+    <t>Canción: "Reconocerme hijo ___"</t>
+  </si>
+  <si>
+    <t>Canción: "Y me diste ___, yo soy tu niña, la niña de tus ojos"</t>
+  </si>
+  <si>
+    <t>Canción: "Solo Dios llena el vacío, ___"</t>
+  </si>
+  <si>
+    <t>Canción: "Que tu ___ me guíe sin fronteras, más allá..."</t>
+  </si>
+  <si>
+    <t>Canción: "Hoy vuelvo a ___, tu nombre Señor..."</t>
+  </si>
+  <si>
+    <t>Canción: "Que mi vida sea para ti como un ___ a tus pies"</t>
+  </si>
+  <si>
+    <t>Canción: "Quiero ser ___ Señor, me cuesta tanto seguirte"</t>
+  </si>
+  <si>
+    <t>Canción: "Rompe esas ___ Espíritu, esas que no dejan concentrar"</t>
+  </si>
+  <si>
+    <t>Canción: "Sumérgeme en el ___ de tu Espíritu"</t>
+  </si>
+  <si>
+    <t>Canción: "Mi corazón, puede sentir tu ___, tú estás aquí"</t>
+  </si>
+  <si>
+    <t>Canción: "Yo veeeengo, a traerte vida en___"</t>
+  </si>
+  <si>
+    <t>Canción: "Vine ___, vine a postrarme"</t>
+  </si>
+  <si>
+    <t>Canción: "Y ligeramente ___ y con un amén contestado"</t>
+  </si>
+  <si>
+    <t>Canción: "Ser sal y luz en este ___"</t>
+  </si>
+  <si>
+    <t>Canción: "Queda oscura ___, tus milagros y tanta fe"</t>
+  </si>
+  <si>
+    <t>Canción: "Y un ___ romperá el cielo desde mi garganta"</t>
+  </si>
+  <si>
+    <t>Canción: "Desligar el creer, del ___"</t>
+  </si>
+  <si>
+    <t>Canción: "Simplemente ___ y déjate de historias"</t>
+  </si>
+  <si>
+    <t>Canción: "A ti te alabo Señor en tu ___"</t>
+  </si>
+  <si>
+    <t>Canción: "Será Dios el que ___ desde el corazón"</t>
+  </si>
+  <si>
+    <t>Canción: "Que se abra el cielo, ___ Señor"</t>
+  </si>
+  <si>
+    <t>Canción: "Hágase mi ___"</t>
+  </si>
+  <si>
+    <t>Canción: "Si amo mi vida, la ___"</t>
+  </si>
+  <si>
+    <t>Canción: "Si fuiste vos quien cargó un madero de ___"</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="13"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F2442"/>
+        <fgColor rgb="FF1F2442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF6D6"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -59,88 +317,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -428,110 +648,495 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C71"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Respuesta</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Pista</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Categoría</t>
-        </is>
-      </c>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="4"/>
+      <c r="B35" s="5"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="4"/>
+      <c r="B36" s="5"/>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="4"/>
+      <c r="B37" s="5"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="4"/>
+      <c r="B38" s="5"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="4"/>
+      <c r="B39" s="5"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="4"/>
+      <c r="B40" s="5"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="4"/>
+      <c r="B41" s="5"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="4"/>
+      <c r="B42" s="5"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="4"/>
+      <c r="B43" s="5"/>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" s="4"/>
+      <c r="B44" s="5"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" s="4"/>
+      <c r="B45" s="5"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" s="4"/>
+      <c r="B46" s="5"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" s="4"/>
+      <c r="B47" s="5"/>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" s="4"/>
+      <c r="B48" s="5"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" s="4"/>
+      <c r="B49" s="5"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" s="4"/>
+      <c r="B50" s="5"/>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" s="4"/>
+      <c r="B51" s="5"/>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" s="4"/>
+      <c r="B52" s="5"/>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" s="4"/>
+      <c r="B53" s="5"/>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" s="4"/>
+      <c r="B54" s="5"/>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" s="4"/>
+      <c r="B55" s="5"/>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" s="4"/>
+      <c r="B56" s="5"/>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" s="4"/>
+      <c r="B57" s="5"/>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" s="4"/>
+      <c r="B58" s="5"/>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" s="4"/>
+      <c r="B59" s="5"/>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" s="4"/>
+      <c r="B60" s="5"/>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" s="6"/>
+      <c r="B61" s="7"/>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" s="6"/>
+      <c r="B62" s="7"/>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" s="6"/>
+      <c r="B63" s="7"/>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" s="6"/>
+      <c r="B64" s="7"/>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" s="6"/>
+      <c r="B65" s="7"/>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" s="6"/>
+      <c r="B66" s="7"/>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" s="6"/>
+      <c r="B67" s="7"/>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" s="6"/>
+      <c r="B68" s="7"/>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" s="6"/>
+      <c r="B69" s="7"/>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" s="6"/>
+      <c r="B70" s="7"/>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" s="6"/>
+      <c r="B71" s="7"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B71">
+    <sortCondition ref="A1:A71"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Pistas propias del crucigrama de la web</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Una pista por fila, en la hoja «Pistas». La primera fila (títulos) no se toca.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Respuesta: la palabra que va en la grilla. Entre 3 y 11 letras. Las tildes y espacios se sacan solos (la Ñ queda).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Pista: lo que lee el jugador. Marcá el hueco con ___ (tres guiones bajos) y dejá palabras después del hueco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Categoría: opcional (por ejemplo «Canciones»). Sirve para ordenar; no se muestra en el juego.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Para publicar: guardá y cerrá este Excel y hacé doble clic en «Actualizar crucigrama.bat» (en la carpeta de la web).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Los crucigramas que ya salieron no cambian: las pistas nuevas aparecen desde mañana.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Si una fila tiene un error (respuesta muy corta o sin pista), el programa la saltea y te avisa qué fila es.</t>
-        </is>
+    <row r="1" spans="1:1" ht="17" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+    </row>
+    <row r="7" spans="1:1" ht="17" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
